--- a/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_0708.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/集群管理故障测试设计_0708.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="112">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -298,11 +298,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>同断网
-不同点：主节点闪断时间小于7s操作成功；超过7s重新选主，选主后各节点数据完整一致；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>catalog主节点网络拥塞</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -329,150 +324,163 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>创建coord节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作过程中异常，coordRG创建成功/失败；
+故障恢复后创建成功的coordRG正常可用，在coordRG创建coord节点创建成功；创建失败可以再次创建；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord处理节点跟catalog编目主节点不在一个主机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM所在主机网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM所在主机网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord处理节点所在主机CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建catalog节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建节点组和节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建dataNode（数据节点）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标节点所在主机CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作过程中异常，节点启动成功/失败；
+故障恢复后重启节点，节点运行正常；连接coord对节点数据做基本操作，操作成功；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord处理节点所在主机内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标节点所在主机内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标节点所在主机时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord处理节点所在主机时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源节点所在主机CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标节点所在主机CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标节点所在主机内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源节点所在主机内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源节点所在主机时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord处理节点所在主机磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标节点所在主机磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源节点所在主机内磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发创建多个dataRG和dataNode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复多次启停coord主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复多次启停catalog主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复多次启停dataNode主节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停止主节点后组内重新选主，重复多次停掉新主并重新启动，各节点数据一致；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停止后启动，节点可正常使用；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点正常/异常重启、主机正常/异常重启,在其他特性都要测试，不单独考虑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间跳变不影响创建节点操作，节点创建成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间跳变不影响节点正常启停，启停成功，节点可以正常使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>同闪断
 不同点：普通拥塞，操作成功；消息拥塞超过7s重新选主，选主后各节点数据完整一致；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>创建coord节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作过程中异常，coordRG创建成功/失败；
-故障恢复后创建成功的coordRG正常可用，在coordRG创建coord节点创建成功；创建失败可以再次创建；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>时间跳变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord处理节点跟catalog编目主节点不在一个主机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM所在主机网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM所在主机网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord处理节点所在主机CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建catalog节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建节点组和节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建dataNode（数据节点）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标节点所在主机CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作过程中异常，节点启动成功/失败；
-故障恢复后重启节点，节点运行正常；连接coord对节点数据做基本操作，操作成功；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord处理节点所在主机内存耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标节点所在主机内存耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标节点所在主机时间跳变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord处理节点所在主机时间跳变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源节点所在主机CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标节点所在主机CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标节点所在主机内存耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源节点所在主机内存耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源节点所在主机时间跳变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord处理节点所在主机磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标节点所在主机磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源节点所在主机内磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>并发创建多个dataRG和dataNode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复多次启停coord主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复多次启停catalog主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复多次启停dataNode主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>停止主节点后组内重新选主，重复多次停掉新主并重新启动，各节点数据一致；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>停止后启动，节点可正常使用；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点正常/异常重启、主机正常/异常重启,在其他特性都要测试，不单独考虑</t>
+    <t>同断网
+不同点：主节点闪断时间小于7s操作成功；超过7s重新选主，选主后各节点数据完整一致；对数据节点做CL等基本操作，操作成功；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1021,7 +1029,7 @@
     </row>
     <row r="2" spans="1:8" s="3" customFormat="1" ht="33.75" customHeight="1">
       <c r="A2" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -1063,7 +1071,7 @@
         <v>27</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H4" s="7"/>
     </row>
@@ -1073,13 +1081,13 @@
       <c r="C5" s="8"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H5" s="7"/>
     </row>
@@ -1117,13 +1125,13 @@
       <c r="C8" s="8"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H8" s="7"/>
     </row>
@@ -1138,7 +1146,7 @@
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
@@ -1177,13 +1185,13 @@
       <c r="C12" s="8"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H12" s="7"/>
     </row>
@@ -1223,13 +1231,13 @@
       <c r="C15" s="8"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H15" s="7"/>
     </row>
@@ -1271,13 +1279,13 @@
       <c r="C18" s="8"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H18" s="7"/>
     </row>
@@ -1317,13 +1325,13 @@
       <c r="C21" s="8"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H21" s="7"/>
     </row>
@@ -1341,13 +1349,13 @@
         <v>32</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>65</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="H22" s="4"/>
     </row>
@@ -1397,13 +1405,13 @@
       <c r="C26" s="8"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H26" s="7"/>
     </row>
@@ -1439,13 +1447,13 @@
       <c r="C29" s="8"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H29" s="7"/>
     </row>
@@ -1485,13 +1493,13 @@
       <c r="C32" s="8"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H32" s="7"/>
     </row>
@@ -1531,13 +1539,13 @@
       <c r="C35" s="8"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H35" s="7"/>
     </row>
@@ -1556,10 +1564,10 @@
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="H36" s="4"/>
     </row>
@@ -1583,13 +1591,13 @@
       <c r="C38" s="8"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H38" s="7"/>
     </row>
@@ -1602,7 +1610,7 @@
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>44</v>
@@ -1627,13 +1635,13 @@
       <c r="C41" s="8"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H41" s="7"/>
     </row>
@@ -1685,13 +1693,13 @@
       <c r="C45" s="8"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H45" s="7"/>
     </row>
@@ -1731,35 +1739,35 @@
       <c r="C48" s="8"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H48" s="7"/>
     </row>
     <row r="49" spans="1:8" ht="40.5">
       <c r="A49" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H49" s="4"/>
     </row>
@@ -1768,11 +1776,11 @@
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
       <c r="D50" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E50" s="7"/>
       <c r="F50" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
@@ -1783,7 +1791,7 @@
       <c r="C51" s="8"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
@@ -1797,7 +1805,7 @@
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
@@ -1807,11 +1815,11 @@
       <c r="B53" s="7"/>
       <c r="C53" s="8"/>
       <c r="D53" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E53" s="7"/>
       <c r="F53" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
@@ -1825,7 +1833,7 @@
       </c>
       <c r="E54" s="7"/>
       <c r="F54" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
@@ -1835,11 +1843,11 @@
       <c r="B55" s="7"/>
       <c r="C55" s="8"/>
       <c r="D55" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E55" s="7"/>
       <c r="F55" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
@@ -1855,10 +1863,10 @@
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H56" s="7"/>
     </row>
@@ -1871,10 +1879,10 @@
       </c>
       <c r="E57" s="7"/>
       <c r="F57" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G57" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>88</v>
       </c>
       <c r="H57" s="7"/>
     </row>
@@ -1887,7 +1895,7 @@
       </c>
       <c r="E58" s="7"/>
       <c r="F58" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
@@ -1901,7 +1909,7 @@
       </c>
       <c r="E59" s="7"/>
       <c r="F59" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
@@ -1915,7 +1923,7 @@
       </c>
       <c r="E60" s="7"/>
       <c r="F60" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
@@ -1929,7 +1937,7 @@
       </c>
       <c r="E61" s="7"/>
       <c r="F61" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
@@ -1942,17 +1950,17 @@
         <v>13</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H62" s="4"/>
     </row>
@@ -1961,11 +1969,11 @@
       <c r="B63" s="7"/>
       <c r="C63" s="8"/>
       <c r="D63" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E63" s="7"/>
       <c r="F63" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
@@ -1979,7 +1987,7 @@
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
@@ -1991,7 +1999,7 @@
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
       <c r="F65" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
@@ -2001,11 +2009,11 @@
       <c r="B66" s="7"/>
       <c r="C66" s="8"/>
       <c r="D66" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
@@ -2019,7 +2027,7 @@
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
@@ -2029,11 +2037,11 @@
       <c r="B68" s="7"/>
       <c r="C68" s="8"/>
       <c r="D68" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
@@ -2049,10 +2057,10 @@
       </c>
       <c r="E69" s="7"/>
       <c r="F69" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H69" s="7"/>
     </row>
@@ -2065,10 +2073,10 @@
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H70" s="7"/>
     </row>
@@ -2081,7 +2089,7 @@
       </c>
       <c r="E71" s="7"/>
       <c r="F71" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
@@ -2095,7 +2103,7 @@
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
@@ -2109,7 +2117,7 @@
       </c>
       <c r="E73" s="7"/>
       <c r="F73" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
@@ -2123,30 +2131,30 @@
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
     </row>
-    <row r="75" spans="1:8" ht="40.5">
+    <row r="75" spans="1:8" ht="27">
       <c r="A75" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E75" s="4"/>
       <c r="F75" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="H75" s="4"/>
     </row>
@@ -2157,7 +2165,7 @@
       <c r="D76" s="7"/>
       <c r="E76" s="7"/>
       <c r="F76" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
@@ -2167,11 +2175,11 @@
       <c r="B77" s="7"/>
       <c r="C77" s="8"/>
       <c r="D77" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E77" s="7"/>
       <c r="F77" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
@@ -2185,7 +2193,7 @@
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
@@ -2195,11 +2203,11 @@
       <c r="B79" s="7"/>
       <c r="C79" s="8"/>
       <c r="D79" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
@@ -2213,7 +2221,7 @@
       </c>
       <c r="E80" s="7"/>
       <c r="F80" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
@@ -2223,16 +2231,16 @@
       <c r="B81" s="7"/>
       <c r="C81" s="8"/>
       <c r="D81" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E81" s="7"/>
       <c r="F81" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:8" ht="40.5">
+    <row r="82" spans="1:8">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="8" t="s">
@@ -2243,10 +2251,10 @@
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="H82" s="7"/>
     </row>
@@ -2259,10 +2267,10 @@
       </c>
       <c r="E83" s="7"/>
       <c r="F83" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H83" s="7"/>
     </row>
@@ -2275,7 +2283,7 @@
       </c>
       <c r="E84" s="7"/>
       <c r="F84" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
@@ -2287,7 +2295,7 @@
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
       <c r="F85" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
@@ -2301,7 +2309,7 @@
       </c>
       <c r="E86" s="7"/>
       <c r="F86" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
@@ -2315,7 +2323,7 @@
       </c>
       <c r="E87" s="7"/>
       <c r="F87" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
@@ -2329,30 +2337,30 @@
       </c>
       <c r="E88" s="7"/>
       <c r="F88" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
     </row>
     <row r="89" spans="1:8" ht="40.5">
       <c r="A89" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E89" s="4"/>
       <c r="F89" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H89" s="4"/>
     </row>
@@ -2361,11 +2369,11 @@
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
       <c r="D90" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E90" s="7"/>
       <c r="F90" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
@@ -2379,7 +2387,7 @@
       </c>
       <c r="E91" s="7"/>
       <c r="F91" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
@@ -2391,7 +2399,7 @@
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
       <c r="F92" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
@@ -2401,11 +2409,11 @@
       <c r="B93" s="7"/>
       <c r="C93" s="8"/>
       <c r="D93" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
@@ -2419,7 +2427,7 @@
       </c>
       <c r="E94" s="7"/>
       <c r="F94" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
@@ -2429,11 +2437,11 @@
       <c r="B95" s="7"/>
       <c r="C95" s="8"/>
       <c r="D95" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E95" s="7"/>
       <c r="F95" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
@@ -2449,10 +2457,10 @@
       </c>
       <c r="E96" s="7"/>
       <c r="F96" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H96" s="7"/>
     </row>
@@ -2465,10 +2473,10 @@
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H97" s="7"/>
     </row>
@@ -2481,7 +2489,7 @@
       </c>
       <c r="E98" s="7"/>
       <c r="F98" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
@@ -2495,7 +2503,7 @@
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
@@ -2509,7 +2517,7 @@
       </c>
       <c r="E100" s="7"/>
       <c r="F100" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
@@ -2523,7 +2531,7 @@
       </c>
       <c r="E101" s="7"/>
       <c r="F101" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
@@ -2536,17 +2544,17 @@
         <v>13</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E102" s="4"/>
       <c r="F102" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H102" s="4"/>
     </row>
@@ -2559,10 +2567,10 @@
       <c r="D103" s="7"/>
       <c r="E103" s="7"/>
       <c r="F103" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H103" s="7"/>
     </row>
@@ -2573,10 +2581,10 @@
       <c r="D104" s="7"/>
       <c r="E104" s="7"/>
       <c r="F104" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G104" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="H104" s="7"/>
     </row>
@@ -2587,22 +2595,22 @@
       <c r="D105" s="7"/>
       <c r="E105" s="7"/>
       <c r="F105" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H105" s="7"/>
     </row>
     <row r="106" spans="1:8" ht="67.5">
       <c r="A106" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
